--- a/rapporten/prijsrapport-2026-04-13.xlsx
+++ b/rapporten/prijsrapport-2026-04-13.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="119">
   <si>
     <t>Product</t>
   </si>
@@ -37,10 +37,10 @@
     <t>Fulfilment</t>
   </si>
   <si>
-    <t>NG Heaven's Body Men Eau de Toilette 100ml -Voor Mannen.</t>
-  </si>
-  <si>
-    <t>8719214753344</t>
+    <t>Real Time - Nuit Charmante - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658360001</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
@@ -49,10 +49,16 @@
     <t>FBR</t>
   </si>
   <si>
-    <t>Sentio Soft Suede Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8721055491453</t>
+    <t>Bubble Bliss Blooming Bella Parfum Giftbag - Eau de parfum voor meisjes 50ml</t>
+  </si>
+  <si>
+    <t>8721055494300</t>
+  </si>
+  <si>
+    <t>Hello Kitty - Giftset - Mermaid Pink - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>8721055493464</t>
   </si>
   <si>
     <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
@@ -64,34 +70,16 @@
     <t>Juwelium</t>
   </si>
   <si>
-    <t>Hello Kitty - Giftset - Rainbow - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>8721055493426</t>
-  </si>
-  <si>
-    <t>Creation Lamis - Espy - Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>5414666016452</t>
-  </si>
-  <si>
-    <t>Omerta -Meet Me Extreme- 100ml Eau de Toilette for men</t>
-  </si>
-  <si>
-    <t>8715658370420</t>
-  </si>
-  <si>
-    <t>NG Lightness Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8719214758363</t>
-  </si>
-  <si>
-    <t>Hello Kitty - Parfum Set Van 6 Stuks - Eau de Parfum Voor Kinderen - 6x15ml</t>
-  </si>
-  <si>
-    <t>8721055493181</t>
+    <t>Creation Lamis Golden Wave Women Giftset</t>
+  </si>
+  <si>
+    <t>6291012002623</t>
+  </si>
+  <si>
+    <t>SENTIO FEESTDAGEN PINK - Merry Christmas And Happy New Year - Body Mist 250ml</t>
+  </si>
+  <si>
+    <t>8721055495970</t>
   </si>
   <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
@@ -109,12 +97,6 @@
     <t>8721055494225</t>
   </si>
   <si>
-    <t>Real Time - Black Rose - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658008354</t>
-  </si>
-  <si>
     <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
   </si>
   <si>
@@ -238,34 +220,28 @@
     <t>Bliksma Retail B.V.</t>
   </si>
   <si>
-    <t>Creation Lamis - Golden Wave - Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>5414666011471</t>
-  </si>
-  <si>
     <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
   </si>
   <si>
     <t>8715658370062</t>
   </si>
   <si>
-    <t>Creation Lamis My Spirit Eau de Parfum For Women 100ml</t>
-  </si>
-  <si>
-    <t>6291012005648</t>
-  </si>
-  <si>
-    <t>Dorall 24 pure for men eau de toilette herenparfum 100ml</t>
-  </si>
-  <si>
-    <t>5414666010511</t>
-  </si>
-  <si>
-    <t>Sentio I Love You Giftset</t>
-  </si>
-  <si>
-    <t>8721055494126</t>
+    <t>Omerta Putting Green Eau de Toilette Pour Homme - 100ml</t>
+  </si>
+  <si>
+    <t>8715658998952</t>
+  </si>
+  <si>
+    <t>Next Generation Touch Desire Eau de Parfum 80ml</t>
+  </si>
+  <si>
+    <t>8719214752699</t>
+  </si>
+  <si>
+    <t>Omerta - Acqua Di Omerta - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658370154</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -783,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -830,19 +806,19 @@
         <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>12.21</v>
+        <v>12.95</v>
       </c>
       <c r="D2" s="1">
-        <v>11.57</v>
+        <v>12.14</v>
       </c>
       <c r="E2" s="1">
-        <v>0.64</v>
+        <v>0.81</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>11.57</v>
+        <v>12.14</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -856,19 +832,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>12.9</v>
+        <v>12.17</v>
       </c>
       <c r="D3" s="1">
-        <v>12.33</v>
+        <v>11.5</v>
       </c>
       <c r="E3" s="1">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>12.33</v>
+        <v>11.5</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -882,19 +858,19 @@
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>9.95</v>
+        <v>12.53</v>
       </c>
       <c r="D4" s="1">
-        <v>9.48</v>
+        <v>11.99</v>
       </c>
       <c r="E4" s="1">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>9.48</v>
+        <v>11.99</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -902,25 +878,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="D5" s="1">
+        <v>9.48</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="1">
-        <v>12.95</v>
-      </c>
-      <c r="D5" s="1">
-        <v>12.53</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.42</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
       <c r="G5" s="1">
-        <v>12.53</v>
+        <v>9.48</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -934,19 +910,19 @@
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>11.87</v>
+        <v>11.95</v>
       </c>
       <c r="D6" s="1">
-        <v>11.5</v>
+        <v>11.56</v>
       </c>
       <c r="E6" s="1">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>11.5</v>
+        <v>11.56</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -960,19 +936,19 @@
         <v>22</v>
       </c>
       <c r="C7" s="1">
-        <v>11.82</v>
+        <v>12.9</v>
       </c>
       <c r="D7" s="1">
-        <v>11.5</v>
+        <v>12.52</v>
       </c>
       <c r="E7" s="1">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>11.5</v>
+        <v>12.52</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -986,19 +962,19 @@
         <v>24</v>
       </c>
       <c r="C8" s="1">
-        <v>11.82</v>
+        <v>5.25</v>
       </c>
       <c r="D8" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="E8" s="1">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G8" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -1006,25 +982,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F9" t="s">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D9" s="1">
-        <v>14.01</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
       <c r="G9" s="1">
-        <v>14.01</v>
+        <v>4.99</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -1032,10 +1008,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>5.25</v>
@@ -1047,7 +1023,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
@@ -1073,7 +1049,7 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
@@ -1090,19 +1066,19 @@
         <v>33</v>
       </c>
       <c r="C12" s="1">
-        <v>11.76</v>
+        <v>5.25</v>
       </c>
       <c r="D12" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="E12" s="1">
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G12" s="1">
-        <v>11.5</v>
+        <v>4.99</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -1125,7 +1101,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -1151,7 +1127,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -1177,7 +1153,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -1203,7 +1179,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1229,7 +1205,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1255,7 +1231,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1281,7 +1257,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1307,7 +1283,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1333,7 +1309,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1359,7 +1335,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1385,7 +1361,7 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
@@ -1411,7 +1387,7 @@
         <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G24" s="1">
         <v>4.99</v>
@@ -1437,7 +1413,7 @@
         <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G25" s="1">
         <v>4.99</v>
@@ -1463,7 +1439,7 @@
         <v>0.26</v>
       </c>
       <c r="F26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
@@ -1489,7 +1465,7 @@
         <v>0.26</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
@@ -1515,7 +1491,7 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G28" s="1">
         <v>4.99</v>
@@ -1532,19 +1508,19 @@
         <v>67</v>
       </c>
       <c r="C29" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D29" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E29" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F29" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="G29" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -1552,25 +1528,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D30" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E30" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F30" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="G30" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1578,25 +1554,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1">
-        <v>5.25</v>
+        <v>11.82</v>
       </c>
       <c r="D31" s="1">
-        <v>4.99</v>
+        <v>11.62</v>
       </c>
       <c r="E31" s="1">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F31" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G31" s="1">
-        <v>4.99</v>
+        <v>11.62</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -1604,25 +1580,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1">
-        <v>9.99</v>
+        <v>12.21</v>
       </c>
       <c r="D32" s="1">
-        <v>9.75</v>
+        <v>12.02</v>
       </c>
       <c r="E32" s="1">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="F32" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>9.75</v>
+        <v>12.02</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -1636,19 +1612,19 @@
         <v>76</v>
       </c>
       <c r="C33" s="1">
-        <v>11.74</v>
+        <v>12.08</v>
       </c>
       <c r="D33" s="1">
-        <v>11.5</v>
+        <v>11.92</v>
       </c>
       <c r="E33" s="1">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="F33" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>11.5</v>
+        <v>11.92</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -1665,16 +1641,16 @@
         <v>9.99</v>
       </c>
       <c r="D34" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="E34" s="1">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G34" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -1688,19 +1664,19 @@
         <v>80</v>
       </c>
       <c r="C35" s="1">
-        <v>13.24</v>
+        <v>9.99</v>
       </c>
       <c r="D35" s="1">
-        <v>13.07</v>
+        <v>9.95</v>
       </c>
       <c r="E35" s="1">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="G35" s="1">
-        <v>13.07</v>
+        <v>9.95</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -1714,19 +1690,19 @@
         <v>82</v>
       </c>
       <c r="C36" s="1">
-        <v>12.8</v>
+        <v>9.99</v>
       </c>
       <c r="D36" s="1">
-        <v>12.67</v>
+        <v>9.95</v>
       </c>
       <c r="E36" s="1">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="G36" s="1">
-        <v>12.67</v>
+        <v>9.95</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -1740,19 +1716,19 @@
         <v>84</v>
       </c>
       <c r="C37" s="1">
-        <v>12.64</v>
+        <v>9.99</v>
       </c>
       <c r="D37" s="1">
-        <v>12.53</v>
+        <v>9.95</v>
       </c>
       <c r="E37" s="1">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="G37" s="1">
-        <v>12.53</v>
+        <v>9.95</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -1775,7 +1751,7 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
@@ -1801,7 +1777,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1827,7 +1803,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1853,7 +1829,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1879,7 +1855,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1905,7 +1881,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1931,7 +1907,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1957,7 +1933,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1983,7 +1959,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -2009,7 +1985,7 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
@@ -2035,7 +2011,7 @@
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G48" s="1">
         <v>9.95</v>
@@ -2061,7 +2037,7 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
@@ -2087,7 +2063,7 @@
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G50" s="1">
         <v>9.95</v>
@@ -2113,7 +2089,7 @@
         <v>0.04</v>
       </c>
       <c r="F51" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G51" s="1">
         <v>9.95</v>
@@ -2139,7 +2115,7 @@
         <v>0.04</v>
       </c>
       <c r="F52" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G52" s="1">
         <v>9.95</v>
@@ -2165,7 +2141,7 @@
         <v>0.04</v>
       </c>
       <c r="F53" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G53" s="1">
         <v>9.95</v>
@@ -2191,116 +2167,12 @@
         <v>0.04</v>
       </c>
       <c r="F54" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G54" s="1">
         <v>9.95</v>
       </c>
       <c r="H54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D55" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E55" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F55" t="s">
-        <v>74</v>
-      </c>
-      <c r="G55" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>121</v>
-      </c>
-      <c r="B56" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D56" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F56" t="s">
-        <v>74</v>
-      </c>
-      <c r="G56" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>123</v>
-      </c>
-      <c r="B57" t="s">
-        <v>124</v>
-      </c>
-      <c r="C57" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D57" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F57" t="s">
-        <v>74</v>
-      </c>
-      <c r="G57" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>125</v>
-      </c>
-      <c r="B58" t="s">
-        <v>126</v>
-      </c>
-      <c r="C58" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D58" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F58" t="s">
-        <v>74</v>
-      </c>
-      <c r="G58" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H58" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-13.xlsx
+++ b/rapporten/prijsrapport-2026-04-13.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="134">
   <si>
     <t>Product</t>
   </si>
@@ -37,10 +37,10 @@
     <t>Fulfilment</t>
   </si>
   <si>
-    <t>Real Time - Nuit Charmante - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658360001</t>
+    <t>Hello Kitty - Giftset - Sweet Leopard - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>7640158817018</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
@@ -49,16 +49,16 @@
     <t>FBR</t>
   </si>
   <si>
-    <t>Bubble Bliss Blooming Bella Parfum Giftbag - Eau de parfum voor meisjes 50ml</t>
-  </si>
-  <si>
-    <t>8721055494300</t>
-  </si>
-  <si>
-    <t>Hello Kitty - Giftset - Mermaid Pink - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>8721055493464</t>
+    <t>Omerta -X Emotion- Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8715658380689</t>
+  </si>
+  <si>
+    <t>SENTIO FEESTDAGEN PINK - Merry Christmas And Happy New Year - Body Mist 250ml</t>
+  </si>
+  <si>
+    <t>8721055495970</t>
   </si>
   <si>
     <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
@@ -70,16 +70,28 @@
     <t>Juwelium</t>
   </si>
   <si>
-    <t>Creation Lamis Golden Wave Women Giftset</t>
-  </si>
-  <si>
-    <t>6291012002623</t>
-  </si>
-  <si>
-    <t>SENTIO FEESTDAGEN PINK - Merry Christmas And Happy New Year - Body Mist 250ml</t>
-  </si>
-  <si>
-    <t>8721055495970</t>
+    <t>Omerta - Out Of Question - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658380412</t>
+  </si>
+  <si>
+    <t>Sentio Chalize Eau De Parfum - 100 ml</t>
+  </si>
+  <si>
+    <t>7640158815694</t>
+  </si>
+  <si>
+    <t>Creation Lamis Ruler Giftset</t>
+  </si>
+  <si>
+    <t>6291012002678</t>
+  </si>
+  <si>
+    <t>Real Time - Me Time - Eau de Toilette - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658350705</t>
   </si>
   <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
@@ -226,22 +238,55 @@
     <t>8715658370062</t>
   </si>
   <si>
-    <t>Omerta Putting Green Eau de Toilette Pour Homme - 100ml</t>
-  </si>
-  <si>
-    <t>8715658998952</t>
-  </si>
-  <si>
-    <t>Next Generation Touch Desire Eau de Parfum 80ml</t>
-  </si>
-  <si>
-    <t>8719214752699</t>
-  </si>
-  <si>
-    <t>Omerta - Acqua Di Omerta - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370154</t>
+    <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>6291012000261</t>
+  </si>
+  <si>
+    <t>Dorsh</t>
+  </si>
+  <si>
+    <t>Real Time - Smart Guy For Men - Eau de toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658350507</t>
+  </si>
+  <si>
+    <t>Savanna Nights - eau de toilette</t>
+  </si>
+  <si>
+    <t>6291012871038</t>
+  </si>
+  <si>
+    <t>Real Time - Blooming Flower Nectar - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658361435</t>
+  </si>
+  <si>
+    <t>Street Looks Miss Important Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8715658340287</t>
+  </si>
+  <si>
+    <t>Sentio Love &amp; Casual for Everyone Eau de Parfum Spray 100 ml</t>
+  </si>
+  <si>
+    <t>8721055493747</t>
+  </si>
+  <si>
+    <t>Real Time - Queen Of Space Blazing Sky - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658360865</t>
+  </si>
+  <si>
+    <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
+  </si>
+  <si>
+    <t>8719214757229</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -759,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -806,19 +851,19 @@
         <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>12.95</v>
+        <v>12.53</v>
       </c>
       <c r="D2" s="1">
-        <v>12.14</v>
+        <v>11.94</v>
       </c>
       <c r="E2" s="1">
-        <v>0.81</v>
+        <v>0.59</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>12.14</v>
+        <v>11.94</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -832,19 +877,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>12.17</v>
+        <v>12.21</v>
       </c>
       <c r="D3" s="1">
-        <v>11.5</v>
+        <v>11.67</v>
       </c>
       <c r="E3" s="1">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>11.5</v>
+        <v>11.67</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -858,19 +903,19 @@
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>12.53</v>
+        <v>12.9</v>
       </c>
       <c r="D4" s="1">
-        <v>11.99</v>
+        <v>12.42</v>
       </c>
       <c r="E4" s="1">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>11.99</v>
+        <v>12.42</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -913,16 +958,16 @@
         <v>11.95</v>
       </c>
       <c r="D6" s="1">
-        <v>11.56</v>
+        <v>11.5</v>
       </c>
       <c r="E6" s="1">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>11.56</v>
+        <v>11.5</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -936,10 +981,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="1">
-        <v>12.9</v>
+        <v>11.95</v>
       </c>
       <c r="D7" s="1">
-        <v>12.52</v>
+        <v>11.57</v>
       </c>
       <c r="E7" s="1">
         <v>0.38</v>
@@ -948,7 +993,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>12.52</v>
+        <v>11.57</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -962,19 +1007,19 @@
         <v>24</v>
       </c>
       <c r="C8" s="1">
-        <v>5.25</v>
+        <v>11.95</v>
       </c>
       <c r="D8" s="1">
-        <v>4.99</v>
+        <v>11.59</v>
       </c>
       <c r="E8" s="1">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>4.99</v>
+        <v>11.59</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -982,25 +1027,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
       <c r="C9" s="1">
-        <v>5.25</v>
+        <v>12.02</v>
       </c>
       <c r="D9" s="1">
-        <v>4.99</v>
+        <v>11.72</v>
       </c>
       <c r="E9" s="1">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>4.99</v>
+        <v>11.72</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -1008,10 +1053,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>5.25</v>
@@ -1023,7 +1068,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
@@ -1049,7 +1094,7 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
@@ -1075,7 +1120,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
@@ -1101,7 +1146,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -1127,7 +1172,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -1153,7 +1198,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -1179,7 +1224,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1205,7 +1250,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1231,7 +1276,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1257,7 +1302,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1283,7 +1328,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1309,7 +1354,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1335,7 +1380,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1361,7 +1406,7 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
@@ -1387,7 +1432,7 @@
         <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G24" s="1">
         <v>4.99</v>
@@ -1413,7 +1458,7 @@
         <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G25" s="1">
         <v>4.99</v>
@@ -1439,7 +1484,7 @@
         <v>0.26</v>
       </c>
       <c r="F26" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
@@ -1465,7 +1510,7 @@
         <v>0.26</v>
       </c>
       <c r="F27" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
@@ -1491,7 +1536,7 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G28" s="1">
         <v>4.99</v>
@@ -1508,19 +1553,19 @@
         <v>67</v>
       </c>
       <c r="C29" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D29" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E29" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F29" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="G29" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -1528,25 +1573,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" t="s">
         <v>69</v>
       </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
       <c r="C30" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D30" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E30" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="G30" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1554,25 +1599,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" t="s">
         <v>71</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D31" s="1">
+        <v>9.75</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="F31" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="1">
-        <v>11.82</v>
-      </c>
-      <c r="D31" s="1">
-        <v>11.62</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
       <c r="G31" s="1">
-        <v>11.62</v>
+        <v>9.75</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -1586,19 +1631,19 @@
         <v>74</v>
       </c>
       <c r="C32" s="1">
-        <v>12.21</v>
+        <v>9.99</v>
       </c>
       <c r="D32" s="1">
-        <v>12.02</v>
+        <v>9.75</v>
       </c>
       <c r="E32" s="1">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G32" s="1">
-        <v>12.02</v>
+        <v>9.75</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -1612,19 +1657,19 @@
         <v>76</v>
       </c>
       <c r="C33" s="1">
-        <v>12.08</v>
+        <v>9.99</v>
       </c>
       <c r="D33" s="1">
-        <v>11.92</v>
+        <v>9.79</v>
       </c>
       <c r="E33" s="1">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="G33" s="1">
-        <v>11.92</v>
+        <v>9.79</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -1632,25 +1677,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1">
-        <v>9.99</v>
+        <v>12.18</v>
       </c>
       <c r="D34" s="1">
-        <v>9.95</v>
+        <v>11.99</v>
       </c>
       <c r="E34" s="1">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="F34" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1">
-        <v>9.95</v>
+        <v>11.99</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -1658,25 +1703,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="1">
-        <v>9.99</v>
+        <v>12.05</v>
       </c>
       <c r="D35" s="1">
-        <v>9.95</v>
+        <v>11.89</v>
       </c>
       <c r="E35" s="1">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="F35" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="G35" s="1">
-        <v>9.95</v>
+        <v>11.89</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -1684,25 +1729,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="1">
-        <v>9.99</v>
+        <v>12.71</v>
       </c>
       <c r="D36" s="1">
-        <v>9.95</v>
+        <v>12.59</v>
       </c>
       <c r="E36" s="1">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F36" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>9.95</v>
+        <v>12.59</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -1710,25 +1755,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1">
-        <v>9.99</v>
+        <v>11.6</v>
       </c>
       <c r="D37" s="1">
-        <v>9.95</v>
+        <v>11.5</v>
       </c>
       <c r="E37" s="1">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="F37" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="G37" s="1">
-        <v>9.95</v>
+        <v>11.5</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -1736,25 +1781,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1">
-        <v>9.99</v>
+        <v>12.17</v>
       </c>
       <c r="D38" s="1">
-        <v>9.95</v>
+        <v>12.1</v>
       </c>
       <c r="E38" s="1">
-        <v>0.04</v>
+        <v>0.07</v>
       </c>
       <c r="F38" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="G38" s="1">
-        <v>9.95</v>
+        <v>12.1</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
@@ -1762,25 +1807,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" s="1">
-        <v>9.99</v>
+        <v>11.87</v>
       </c>
       <c r="D39" s="1">
-        <v>9.95</v>
+        <v>11.82</v>
       </c>
       <c r="E39" s="1">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F39" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="G39" s="1">
-        <v>9.95</v>
+        <v>11.82</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
@@ -1788,25 +1833,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" s="1">
         <v>9.99</v>
       </c>
       <c r="D40" s="1">
-        <v>9.95</v>
+        <v>9.94</v>
       </c>
       <c r="E40" s="1">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F40" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G40" s="1">
-        <v>9.95</v>
+        <v>9.94</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
@@ -1814,10 +1859,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1">
         <v>9.99</v>
@@ -1829,7 +1874,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1840,10 +1885,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" s="1">
         <v>9.99</v>
@@ -1855,7 +1900,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1866,10 +1911,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" s="1">
         <v>9.99</v>
@@ -1881,7 +1926,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1892,10 +1937,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1">
         <v>9.99</v>
@@ -1907,7 +1952,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1918,10 +1963,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C45" s="1">
         <v>9.99</v>
@@ -1933,7 +1978,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1944,10 +1989,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1">
         <v>9.99</v>
@@ -1959,7 +2004,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -1970,10 +2015,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1">
         <v>9.99</v>
@@ -1985,7 +2030,7 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
@@ -1996,10 +2041,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1">
         <v>9.99</v>
@@ -2011,7 +2056,7 @@
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G48" s="1">
         <v>9.95</v>
@@ -2022,10 +2067,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1">
         <v>9.99</v>
@@ -2037,7 +2082,7 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
@@ -2048,10 +2093,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1">
         <v>9.99</v>
@@ -2063,7 +2108,7 @@
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G50" s="1">
         <v>9.95</v>
@@ -2074,10 +2119,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1">
         <v>9.99</v>
@@ -2089,7 +2134,7 @@
         <v>0.04</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G51" s="1">
         <v>9.95</v>
@@ -2100,10 +2145,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C52" s="1">
         <v>9.99</v>
@@ -2115,7 +2160,7 @@
         <v>0.04</v>
       </c>
       <c r="F52" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G52" s="1">
         <v>9.95</v>
@@ -2126,10 +2171,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C53" s="1">
         <v>9.99</v>
@@ -2141,7 +2186,7 @@
         <v>0.04</v>
       </c>
       <c r="F53" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G53" s="1">
         <v>9.95</v>
@@ -2152,10 +2197,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C54" s="1">
         <v>9.99</v>
@@ -2167,12 +2212,194 @@
         <v>0.04</v>
       </c>
       <c r="F54" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G54" s="1">
         <v>9.95</v>
       </c>
       <c r="H54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D55" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F55" t="s">
+        <v>72</v>
+      </c>
+      <c r="G55" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D56" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F56" t="s">
+        <v>72</v>
+      </c>
+      <c r="G56" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D57" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F57" t="s">
+        <v>72</v>
+      </c>
+      <c r="G57" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D58" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F58" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D59" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F59" t="s">
+        <v>72</v>
+      </c>
+      <c r="G59" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D60" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F60" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D61" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F61" t="s">
+        <v>72</v>
+      </c>
+      <c r="G61" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H61" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-13.xlsx
+++ b/rapporten/prijsrapport-2026-04-13.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="122">
   <si>
     <t>Product</t>
   </si>
@@ -37,10 +37,10 @@
     <t>Fulfilment</t>
   </si>
   <si>
-    <t>Hello Kitty - Giftset - Sweet Leopard - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>7640158817018</t>
+    <t>Creation Lamis - Golden Wave for him - Eau de Toilette 100ml</t>
+  </si>
+  <si>
+    <t>5414666009485</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
@@ -49,16 +49,22 @@
     <t>FBR</t>
   </si>
   <si>
-    <t>Omerta -X Emotion- Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658380689</t>
-  </si>
-  <si>
-    <t>SENTIO FEESTDAGEN PINK - Merry Christmas And Happy New Year - Body Mist 250ml</t>
-  </si>
-  <si>
-    <t>8721055495970</t>
+    <t>Catsuit Man parfum - Heren eau de toilette met munt, lavendel en bergamot</t>
+  </si>
+  <si>
+    <t>8719992723812</t>
+  </si>
+  <si>
+    <t>Omerta Express Sensualite Frivole 100ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8715658380238</t>
+  </si>
+  <si>
+    <t>Omerta - Faktz Select - Eau De Toilette - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658370215</t>
   </si>
   <si>
     <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
@@ -70,28 +76,16 @@
     <t>Juwelium</t>
   </si>
   <si>
-    <t>Omerta - Out Of Question - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658380412</t>
-  </si>
-  <si>
-    <t>Sentio Chalize Eau De Parfum - 100 ml</t>
-  </si>
-  <si>
-    <t>7640158815694</t>
-  </si>
-  <si>
-    <t>Creation Lamis Ruler Giftset</t>
-  </si>
-  <si>
-    <t>6291012002678</t>
-  </si>
-  <si>
-    <t>Real Time - Me Time - Eau de Toilette - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658350705</t>
+    <t>SENTIO FEESTDAGEN PINK - Warm Wishes! And Cozy Kisses - Body Mist 250ml</t>
+  </si>
+  <si>
+    <t>8721055492603</t>
+  </si>
+  <si>
+    <t>Street Looks - Fleurette - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658013006</t>
   </si>
   <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
@@ -238,55 +232,25 @@
     <t>8715658370062</t>
   </si>
   <si>
-    <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>6291012000261</t>
+    <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
+  </si>
+  <si>
+    <t>8719214757229</t>
   </si>
   <si>
     <t>Dorsh</t>
   </si>
   <si>
-    <t>Real Time - Smart Guy For Men - Eau de toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658350507</t>
-  </si>
-  <si>
-    <t>Savanna Nights - eau de toilette</t>
-  </si>
-  <si>
-    <t>6291012871038</t>
-  </si>
-  <si>
-    <t>Real Time - Blooming Flower Nectar - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658361435</t>
-  </si>
-  <si>
-    <t>Street Looks Miss Important Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658340287</t>
-  </si>
-  <si>
-    <t>Sentio Love &amp; Casual for Everyone Eau de Parfum Spray 100 ml</t>
-  </si>
-  <si>
-    <t>8721055493747</t>
-  </si>
-  <si>
-    <t>Real Time - Queen Of Space Blazing Sky - Eau De Parfum - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658360865</t>
-  </si>
-  <si>
-    <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
-  </si>
-  <si>
-    <t>8719214757229</t>
+    <t>Omerta - Sweet Pommy - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658998563</t>
+  </si>
+  <si>
+    <t>Dorall Lancy parfum Eau de Toilette voor haar - Zwarte bes, Peer, Iris - 100ml</t>
+  </si>
+  <si>
+    <t>5414666016216</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -804,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -851,19 +815,19 @@
         <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>12.53</v>
+        <v>13.88</v>
       </c>
       <c r="D2" s="1">
-        <v>11.94</v>
+        <v>13.24</v>
       </c>
       <c r="E2" s="1">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>11.94</v>
+        <v>13.24</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -877,19 +841,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>12.21</v>
+        <v>14.75</v>
       </c>
       <c r="D3" s="1">
-        <v>11.67</v>
+        <v>14.15</v>
       </c>
       <c r="E3" s="1">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>11.67</v>
+        <v>14.15</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -903,19 +867,19 @@
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>12.9</v>
+        <v>12.08</v>
       </c>
       <c r="D4" s="1">
-        <v>12.42</v>
+        <v>11.5</v>
       </c>
       <c r="E4" s="1">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>12.42</v>
+        <v>11.5</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -929,19 +893,19 @@
         <v>17</v>
       </c>
       <c r="C5" s="1">
-        <v>9.95</v>
+        <v>12.08</v>
       </c>
       <c r="D5" s="1">
-        <v>9.48</v>
+        <v>11.5</v>
       </c>
       <c r="E5" s="1">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>9.48</v>
+        <v>11.5</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -949,25 +913,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="D6" s="1">
+        <v>9.48</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="F6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="1">
-        <v>11.95</v>
-      </c>
-      <c r="D6" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
       <c r="G6" s="1">
-        <v>11.5</v>
+        <v>9.48</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -981,19 +945,19 @@
         <v>22</v>
       </c>
       <c r="C7" s="1">
-        <v>11.95</v>
+        <v>11.84</v>
       </c>
       <c r="D7" s="1">
-        <v>11.57</v>
+        <v>11.5</v>
       </c>
       <c r="E7" s="1">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>11.57</v>
+        <v>11.5</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -1007,19 +971,19 @@
         <v>24</v>
       </c>
       <c r="C8" s="1">
-        <v>11.95</v>
+        <v>11.97</v>
       </c>
       <c r="D8" s="1">
-        <v>11.59</v>
+        <v>11.67</v>
       </c>
       <c r="E8" s="1">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>11.59</v>
+        <v>11.67</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -1033,19 +997,19 @@
         <v>26</v>
       </c>
       <c r="C9" s="1">
-        <v>12.02</v>
+        <v>5.25</v>
       </c>
       <c r="D9" s="1">
-        <v>11.72</v>
+        <v>4.99</v>
       </c>
       <c r="E9" s="1">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G9" s="1">
-        <v>11.72</v>
+        <v>4.99</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -1053,10 +1017,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>5.25</v>
@@ -1068,7 +1032,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
@@ -1094,7 +1058,7 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
@@ -1120,7 +1084,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
@@ -1146,7 +1110,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -1172,7 +1136,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -1198,7 +1162,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -1224,7 +1188,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1250,7 +1214,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1276,7 +1240,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1302,7 +1266,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1328,7 +1292,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1354,7 +1318,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1380,7 +1344,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1406,7 +1370,7 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
@@ -1432,7 +1396,7 @@
         <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G24" s="1">
         <v>4.99</v>
@@ -1458,7 +1422,7 @@
         <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G25" s="1">
         <v>4.99</v>
@@ -1484,7 +1448,7 @@
         <v>0.26</v>
       </c>
       <c r="F26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
@@ -1510,7 +1474,7 @@
         <v>0.26</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
@@ -1536,7 +1500,7 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G28" s="1">
         <v>4.99</v>
@@ -1562,7 +1526,7 @@
         <v>0.26</v>
       </c>
       <c r="F29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G29" s="1">
         <v>4.99</v>
@@ -1579,19 +1543,19 @@
         <v>69</v>
       </c>
       <c r="C30" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D30" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E30" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F30" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="G30" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1599,10 +1563,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1">
         <v>9.99</v>
@@ -1614,7 +1578,7 @@
         <v>0.24</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G31" s="1">
         <v>9.75</v>
@@ -1634,16 +1598,16 @@
         <v>9.99</v>
       </c>
       <c r="D32" s="1">
-        <v>9.75</v>
+        <v>9.79</v>
       </c>
       <c r="E32" s="1">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="F32" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G32" s="1">
-        <v>9.75</v>
+        <v>9.79</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -1651,25 +1615,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" s="1">
-        <v>9.99</v>
+        <v>12.49</v>
       </c>
       <c r="D33" s="1">
-        <v>9.79</v>
+        <v>12.38</v>
       </c>
       <c r="E33" s="1">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="F33" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>9.79</v>
+        <v>12.38</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -1683,19 +1647,19 @@
         <v>79</v>
       </c>
       <c r="C34" s="1">
-        <v>12.18</v>
+        <v>11.89</v>
       </c>
       <c r="D34" s="1">
-        <v>11.99</v>
+        <v>11.84</v>
       </c>
       <c r="E34" s="1">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="F34" t="s">
         <v>10</v>
       </c>
       <c r="G34" s="1">
-        <v>11.99</v>
+        <v>11.84</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -1709,19 +1673,19 @@
         <v>81</v>
       </c>
       <c r="C35" s="1">
-        <v>12.05</v>
+        <v>9.99</v>
       </c>
       <c r="D35" s="1">
-        <v>11.89</v>
+        <v>9.95</v>
       </c>
       <c r="E35" s="1">
-        <v>0.16</v>
+        <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G35" s="1">
-        <v>11.89</v>
+        <v>9.95</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -1735,19 +1699,19 @@
         <v>83</v>
       </c>
       <c r="C36" s="1">
-        <v>12.71</v>
+        <v>9.99</v>
       </c>
       <c r="D36" s="1">
-        <v>12.59</v>
+        <v>9.95</v>
       </c>
       <c r="E36" s="1">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G36" s="1">
-        <v>12.59</v>
+        <v>9.95</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -1761,19 +1725,19 @@
         <v>85</v>
       </c>
       <c r="C37" s="1">
-        <v>11.6</v>
+        <v>9.99</v>
       </c>
       <c r="D37" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="E37" s="1">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G37" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -1787,19 +1751,19 @@
         <v>87</v>
       </c>
       <c r="C38" s="1">
-        <v>12.17</v>
+        <v>9.99</v>
       </c>
       <c r="D38" s="1">
-        <v>12.1</v>
+        <v>9.95</v>
       </c>
       <c r="E38" s="1">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G38" s="1">
-        <v>12.1</v>
+        <v>9.95</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
@@ -1813,19 +1777,19 @@
         <v>89</v>
       </c>
       <c r="C39" s="1">
-        <v>11.87</v>
+        <v>9.99</v>
       </c>
       <c r="D39" s="1">
-        <v>11.82</v>
+        <v>9.95</v>
       </c>
       <c r="E39" s="1">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G39" s="1">
-        <v>11.82</v>
+        <v>9.95</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
@@ -1842,16 +1806,16 @@
         <v>9.99</v>
       </c>
       <c r="D40" s="1">
-        <v>9.94</v>
+        <v>9.95</v>
       </c>
       <c r="E40" s="1">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G40" s="1">
-        <v>9.94</v>
+        <v>9.95</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
@@ -1874,7 +1838,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1900,7 +1864,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1926,7 +1890,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1952,7 +1916,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1978,7 +1942,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -2004,7 +1968,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -2030,7 +1994,7 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
@@ -2056,7 +2020,7 @@
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G48" s="1">
         <v>9.95</v>
@@ -2082,7 +2046,7 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
@@ -2108,7 +2072,7 @@
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G50" s="1">
         <v>9.95</v>
@@ -2134,7 +2098,7 @@
         <v>0.04</v>
       </c>
       <c r="F51" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G51" s="1">
         <v>9.95</v>
@@ -2160,7 +2124,7 @@
         <v>0.04</v>
       </c>
       <c r="F52" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G52" s="1">
         <v>9.95</v>
@@ -2186,7 +2150,7 @@
         <v>0.04</v>
       </c>
       <c r="F53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G53" s="1">
         <v>9.95</v>
@@ -2212,7 +2176,7 @@
         <v>0.04</v>
       </c>
       <c r="F54" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G54" s="1">
         <v>9.95</v>
@@ -2238,168 +2202,12 @@
         <v>0.04</v>
       </c>
       <c r="F55" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G55" s="1">
         <v>9.95</v>
       </c>
       <c r="H55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D56" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F56" t="s">
-        <v>72</v>
-      </c>
-      <c r="G56" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" t="s">
-        <v>125</v>
-      </c>
-      <c r="C57" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D57" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F57" t="s">
-        <v>72</v>
-      </c>
-      <c r="G57" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" t="s">
-        <v>127</v>
-      </c>
-      <c r="C58" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D58" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F58" t="s">
-        <v>72</v>
-      </c>
-      <c r="G58" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H58" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>128</v>
-      </c>
-      <c r="B59" t="s">
-        <v>129</v>
-      </c>
-      <c r="C59" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D59" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E59" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F59" t="s">
-        <v>72</v>
-      </c>
-      <c r="G59" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>130</v>
-      </c>
-      <c r="B60" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D60" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F60" t="s">
-        <v>72</v>
-      </c>
-      <c r="G60" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>132</v>
-      </c>
-      <c r="B61" t="s">
-        <v>133</v>
-      </c>
-      <c r="C61" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D61" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E61" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F61" t="s">
-        <v>72</v>
-      </c>
-      <c r="G61" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H61" t="s">
         <v>11</v>
       </c>
     </row>
